--- a/data/applications/applications.xlsx
+++ b/data/applications/applications.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:S3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,9 +517,68 @@
         <v/>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Panthadip Maji</v>
+      </c>
+      <c r="B3" t="str">
+        <v>majipanthadip@gmail.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>1772926457704-754730388.pdf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>1772926476793-470080063.webm</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="G3" t="str">
+        <v>12.97736531081203</v>
+      </c>
+      <c r="H3" t="str">
+        <v>77.66594146593036</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>daint01</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Data Analyst Intern</v>
+      </c>
+      <c r="M3" t="str">
+        <v>2026-03-07T23:34:24.427Z</v>
+      </c>
+      <c r="N3" t="str">
+        <v>1tPsV3IwHx0opL0elQnhBsk1f9A4-UwUg</v>
+      </c>
+      <c r="O3" t="str">
+        <v>https://drive.google.com/file/d/1tPsV3IwHx0opL0elQnhBsk1f9A4-UwUg/view?usp=drivesdk</v>
+      </c>
+      <c r="P3" t="str">
+        <v>1zWAMSLizgpZJGYiMXr5T00IpDH2fssya</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>https://drive.google.com/file/d/1zWAMSLizgpZJGYiMXr5T00IpDH2fssya/view?usp=drivesdk</v>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/applications/applications.xlsx
+++ b/data/applications/applications.xlsx
@@ -1,41 +1,89 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PANTHADIP MAJI\Downloads\quantedge-portal\data\applications\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D86CB536-1D40-4137-93BA-961CED8688FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>ResumePath</t>
+  </si>
+  <si>
+    <t>AudioPath</t>
+  </si>
+  <si>
+    <t>PhotoPath</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>Lat</t>
+  </si>
+  <si>
+    <t>Lon</t>
+  </si>
+  <si>
+    <t>TestScore</t>
+  </si>
+  <si>
+    <t>TestAnswers</t>
+  </si>
+  <si>
+    <t>JobCode</t>
+  </si>
+  <si>
+    <t>JobTitle</t>
+  </si>
+  <si>
+    <t>AppliedAt</t>
+  </si>
+  <si>
+    <t>ResumeDriveId</t>
+  </si>
+  <si>
+    <t>ResumeDriveLink</t>
+  </si>
+  <si>
+    <t>AudioDriveId</t>
+  </si>
+  <si>
+    <t>AudioDriveLink</t>
+  </si>
+  <si>
+    <t>PhotoDriveId</t>
+  </si>
+  <si>
+    <t>PhotoDriveLink</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +113,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,189 +452,73 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Email</v>
-      </c>
-      <c r="C1" t="str">
-        <v>ResumePath</v>
-      </c>
-      <c r="D1" t="str">
-        <v>AudioPath</v>
-      </c>
-      <c r="E1" t="str">
-        <v>PhotoPath</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Office</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Lat</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Lon</v>
-      </c>
-      <c r="I1" t="str">
-        <v>TestScore</v>
-      </c>
-      <c r="J1" t="str">
-        <v>TestAnswers</v>
-      </c>
-      <c r="K1" t="str">
-        <v>JobCode</v>
-      </c>
-      <c r="L1" t="str">
-        <v>JobTitle</v>
-      </c>
-      <c r="M1" t="str">
-        <v>AppliedAt</v>
-      </c>
-      <c r="N1" t="str">
-        <v>ResumeDriveId</v>
-      </c>
-      <c r="O1" t="str">
-        <v>ResumeDriveLink</v>
-      </c>
-      <c r="P1" t="str">
-        <v>AudioDriveId</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>AudioDriveLink</v>
-      </c>
-      <c r="R1" t="str">
-        <v>PhotoDriveId</v>
-      </c>
-      <c r="S1" t="str">
-        <v>PhotoDriveLink</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Panthadip Maji</v>
-      </c>
-      <c r="B2" t="str">
-        <v>majipanthadip@gmail.com</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1772917548754-251139681.pdf</v>
-      </c>
-      <c r="D2" t="str">
-        <v>1772917578278-998959388.webm</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-      <c r="F2" t="str">
-        <v>Hyderabad</v>
-      </c>
-      <c r="G2" t="str">
-        <v>12.977332181054091</v>
-      </c>
-      <c r="H2" t="str">
-        <v>77.6659081661621</v>
-      </c>
-      <c r="I2">
+    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="J2" t="str">
-        <v>[{"qid":1,"answer":1},{"qid":2,"answer":0},{"qid":3,"answer":0},{"qid":4,"answer":0},{"qid":5,"answer":2},{"qid":6,"answer":2},{"qid":7,"answer":3},{"qid":8,"answer":2},{"qid":9,"answer":1},{"qid":10,"answer":0},{"qid":11,"answer":0},{"qid":12,"answer":0},{"qid":13,"answer":0},{"qid":14,"answer":1},{"qid":15,"answer":1},{"qid":16,"answer":1},{"qid":17,"answer":2},{"qid":18,"answer":2},{"qid":19,"answer":1},{"qid":20,"answer":2}]</v>
-      </c>
-      <c r="K2" t="str">
-        <v>dafresher02</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Data Analyst (Fresher)</v>
-      </c>
-      <c r="M2" t="str">
-        <v>2026-03-07T21:05:55.218Z</v>
-      </c>
-      <c r="N2" t="str">
-        <v>1rVJqWlxKIqwfuRgbBn3Pq4AfkQ8cmZqr</v>
-      </c>
-      <c r="O2" t="str">
-        <v>https://drive.google.com/file/d/1rVJqWlxKIqwfuRgbBn3Pq4AfkQ8cmZqr/view?usp=drivesdk</v>
-      </c>
-      <c r="P2" t="str">
-        <v>1FBvI2g29XraQ82X3rOEh0VleumMicRAW</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>https://drive.google.com/file/d/1FBvI2g29XraQ82X3rOEh0VleumMicRAW/view?usp=drivesdk</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Panthadip Maji</v>
-      </c>
-      <c r="B3" t="str">
-        <v>majipanthadip@gmail.com</v>
-      </c>
-      <c r="C3" t="str">
-        <v>1772926457704-754730388.pdf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>1772926476793-470080063.webm</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="G3" t="str">
-        <v>12.97736531081203</v>
-      </c>
-      <c r="H3" t="str">
-        <v>77.66594146593036</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>daint01</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Data Analyst Intern</v>
-      </c>
-      <c r="M3" t="str">
-        <v>2026-03-07T23:34:24.427Z</v>
-      </c>
-      <c r="N3" t="str">
-        <v>1tPsV3IwHx0opL0elQnhBsk1f9A4-UwUg</v>
-      </c>
-      <c r="O3" t="str">
-        <v>https://drive.google.com/file/d/1tPsV3IwHx0opL0elQnhBsk1f9A4-UwUg/view?usp=drivesdk</v>
-      </c>
-      <c r="P3" t="str">
-        <v>1zWAMSLizgpZJGYiMXr5T00IpDH2fssya</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>https://drive.google.com/file/d/1zWAMSLizgpZJGYiMXr5T00IpDH2fssya/view?usp=drivesdk</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S3"/>
+    <ignoredError sqref="A1:S1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>